--- a/Dataset/Alphabets-Dataset/burushaski-characters.xlsx
+++ b/Dataset/Alphabets-Dataset/burushaski-characters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Sardar Ali\personal data\University\Burushaski\Alphabets-Dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SARDAR ALI\Git\Burushaski\Dataset\Alphabets-Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,10 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="166">
-  <si>
-    <t>Character</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="172">
   <si>
     <t>Unicode</t>
   </si>
@@ -518,10 +515,31 @@
     <t>Romanization</t>
   </si>
   <si>
-    <t>Example_Word</t>
-  </si>
-  <si>
     <t>/a/</t>
+  </si>
+  <si>
+    <t>Roman</t>
+  </si>
+  <si>
+    <t>Nastaliq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example_word_Nastaliq </t>
+  </si>
+  <si>
+    <t>Example_word_Roman</t>
+  </si>
+  <si>
+    <t>Gloss_EN</t>
+  </si>
+  <si>
+    <t>اسقور</t>
+  </si>
+  <si>
+    <t>aasqor</t>
+  </si>
+  <si>
+    <t>flower</t>
   </si>
 </sst>
 </file>
@@ -1005,1231 +1023,1423 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
-    <col min="2" max="2" width="20.109375" customWidth="1"/>
-    <col min="3" max="5" width="29.109375" customWidth="1"/>
-    <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="7" max="8" width="27.88671875" customWidth="1"/>
-    <col min="9" max="9" width="28.44140625" customWidth="1"/>
-    <col min="10" max="10" width="49.88671875" customWidth="1"/>
+    <col min="2" max="3" width="20.109375" customWidth="1"/>
+    <col min="4" max="9" width="29.109375" customWidth="1"/>
+    <col min="10" max="10" width="27" customWidth="1"/>
+    <col min="11" max="11" width="27.88671875" customWidth="1"/>
+    <col min="12" max="12" width="28.44140625" customWidth="1"/>
+    <col min="13" max="13" width="49.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="20" customFormat="1" ht="15.6">
+    <row r="1" spans="1:13" s="20" customFormat="1" ht="15.6">
       <c r="A1" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="28.2">
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2">
+        <v>627</v>
+      </c>
+      <c r="F2" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="B1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="E1" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="F1" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="I1" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="21" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="28.2">
-      <c r="B2" s="1" t="s">
+      <c r="G2" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="J2" s="3"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="28.2">
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2">
-        <v>627</v>
-      </c>
-      <c r="E2" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="28.2">
-      <c r="B3" s="1" t="s">
+      <c r="J3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="K3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="L3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="6" t="s">
+    </row>
+    <row r="4" spans="1:13" ht="28.2">
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="28.2">
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1"/>
+      <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="6" t="s">
+    </row>
+    <row r="5" spans="1:13" ht="28.2">
+      <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="28.2">
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1"/>
+      <c r="D5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J5" s="6" t="s">
+    </row>
+    <row r="6" spans="1:13" ht="28.2">
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="28.2">
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J6" s="6" t="s">
+    </row>
+    <row r="7" spans="1:13" ht="28.2">
+      <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="28.2">
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1"/>
+      <c r="D7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J7" s="6" t="s">
+    </row>
+    <row r="8" spans="1:13" ht="28.2">
+      <c r="B8" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="28.2">
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1"/>
+      <c r="D8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" s="6" t="s">
+    </row>
+    <row r="9" spans="1:13" ht="28.2">
+      <c r="B9" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="28.2">
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1"/>
+      <c r="D9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="6" t="s">
+    </row>
+    <row r="10" spans="1:13" ht="28.2">
+      <c r="B10" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="28.2">
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1"/>
+      <c r="D10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="6" t="s">
+    </row>
+    <row r="11" spans="1:13" ht="28.2">
+      <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="28.2">
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1"/>
+      <c r="D11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="5" t="s">
+      <c r="M11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="6" t="s">
+    </row>
+    <row r="12" spans="1:13" ht="28.2">
+      <c r="B12" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="28.2">
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1"/>
+      <c r="D12" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="6" t="s">
+    </row>
+    <row r="13" spans="1:13" ht="28.2">
+      <c r="B13" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="28.2">
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1"/>
+      <c r="D13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J13" s="6" t="s">
+    </row>
+    <row r="14" spans="1:13" ht="28.2">
+      <c r="B14" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="28.2">
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1"/>
+      <c r="D14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M14" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="6" t="s">
+    </row>
+    <row r="15" spans="1:13" ht="28.2">
+      <c r="B15" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="28.2">
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1"/>
+      <c r="D15" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M15" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="6" t="s">
+    </row>
+    <row r="16" spans="1:13" ht="28.2">
+      <c r="B16" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="28.2">
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1"/>
+      <c r="D16" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M16" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="6" t="s">
+    </row>
+    <row r="17" spans="2:13" ht="28.2">
+      <c r="B17" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="17" spans="2:10" ht="28.2">
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1"/>
+      <c r="D17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M17" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J17" s="6" t="s">
+    </row>
+    <row r="18" spans="2:13" ht="28.2">
+      <c r="B18" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="18" spans="2:10" ht="28.2">
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1"/>
+      <c r="D18" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="3" t="s">
+      <c r="K18" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="L18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M18" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="6" t="s">
+    </row>
+    <row r="19" spans="2:13" ht="28.2">
+      <c r="B19" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="19" spans="2:10" ht="28.2">
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1"/>
+      <c r="D19" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M19" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J19" s="6" t="s">
+    </row>
+    <row r="20" spans="2:13" ht="28.2">
+      <c r="B20" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="20" spans="2:10" ht="28.2">
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1"/>
+      <c r="D20" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M20" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="6" t="s">
+    </row>
+    <row r="21" spans="2:13" ht="28.2">
+      <c r="B21" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="21" spans="2:10" ht="28.2">
-      <c r="B21" s="1" t="s">
+      <c r="C21" s="1"/>
+      <c r="D21" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M21" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J21" s="6" t="s">
+    </row>
+    <row r="22" spans="2:13" ht="28.2">
+      <c r="B22" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="22" spans="2:10" ht="28.2">
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1"/>
+      <c r="D22" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M22" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="6" t="s">
+    </row>
+    <row r="23" spans="2:13" ht="28.2">
+      <c r="B23" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="23" spans="2:10" ht="28.2">
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1"/>
+      <c r="D23" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M23" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J23" s="6" t="s">
+    </row>
+    <row r="24" spans="2:13" ht="28.2">
+      <c r="B24" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="24" spans="2:10" ht="28.2">
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="1"/>
+      <c r="D24" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M24" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J24" s="6" t="s">
+    </row>
+    <row r="25" spans="2:13" ht="28.2">
+      <c r="B25" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="25" spans="2:10" ht="28.2">
-      <c r="B25" s="1" t="s">
+      <c r="C25" s="1"/>
+      <c r="D25" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M25" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J25" s="6" t="s">
+    </row>
+    <row r="26" spans="2:13" ht="28.2">
+      <c r="B26" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="26" spans="2:10" ht="28.2">
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1"/>
+      <c r="D26" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M26" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J26" s="6" t="s">
+    </row>
+    <row r="27" spans="2:13" ht="28.2">
+      <c r="B27" s="1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="27" spans="2:10" ht="28.2">
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1"/>
+      <c r="D27" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M27" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J27" s="6" t="s">
+    </row>
+    <row r="28" spans="2:13" ht="28.2">
+      <c r="B28" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="28" spans="2:10" ht="28.2">
-      <c r="B28" s="1" t="s">
+      <c r="C28" s="1"/>
+      <c r="D28" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M28" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J28" s="6" t="s">
+    </row>
+    <row r="29" spans="2:13" ht="28.2">
+      <c r="B29" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="29" spans="2:10" ht="28.2">
-      <c r="B29" s="1" t="s">
+      <c r="C29" s="1"/>
+      <c r="D29" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M29" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J29" s="6" t="s">
+    </row>
+    <row r="30" spans="2:13" ht="28.2">
+      <c r="B30" s="11" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="30" spans="2:10" ht="28.2">
-      <c r="B30" s="11" t="s">
+      <c r="C30" s="11"/>
+      <c r="D30" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="9" t="s">
+      <c r="K30" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="G30" s="8" t="s">
+      <c r="L30" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M30" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="H30" s="8"/>
-      <c r="I30" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J30" s="6" t="s">
+    </row>
+    <row r="31" spans="2:13" ht="28.2">
+      <c r="B31" s="11" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="31" spans="2:10" ht="28.2">
-      <c r="B31" s="11" t="s">
+      <c r="C31" s="11"/>
+      <c r="D31" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="K31" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G31" s="8" t="s">
+      <c r="L31" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M31" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="H31" s="8"/>
-      <c r="I31" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J31" s="6" t="s">
+    </row>
+    <row r="32" spans="2:13" ht="28.2">
+      <c r="B32" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="32" spans="2:10" ht="28.2">
-      <c r="B32" s="1" t="s">
+      <c r="C32" s="1"/>
+      <c r="D32" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M32" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J32" s="6" t="s">
+    </row>
+    <row r="33" spans="2:13" ht="28.2">
+      <c r="B33" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="33" spans="2:10" ht="28.2">
-      <c r="B33" s="1" t="s">
+      <c r="C33" s="1"/>
+      <c r="D33" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M33" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J33" s="6" t="s">
+    </row>
+    <row r="34" spans="2:13" ht="28.2">
+      <c r="B34" s="11" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="34" spans="2:10" ht="28.2">
-      <c r="B34" s="11" t="s">
+      <c r="C34" s="11"/>
+      <c r="D34" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="K34" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M34" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="G34" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="H34" s="12"/>
-      <c r="I34" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J34" s="6" t="s">
+    </row>
+    <row r="35" spans="2:13" ht="28.2">
+      <c r="B35" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="35" spans="2:10" ht="28.2">
-      <c r="B35" s="1" t="s">
+      <c r="C35" s="1"/>
+      <c r="D35" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M35" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J35" s="6" t="s">
+    </row>
+    <row r="36" spans="2:13" ht="28.2">
+      <c r="B36" s="11" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="36" spans="2:10" ht="28.2">
-      <c r="B36" s="11" t="s">
+      <c r="C36" s="11"/>
+      <c r="D36" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K36" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="L36" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="M36" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G36" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="H36" s="12"/>
-      <c r="I36" s="5" t="s">
+    </row>
+    <row r="37" spans="2:13" ht="28.2">
+      <c r="B37" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="J36" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" ht="28.2">
-      <c r="B37" s="13" t="s">
+      <c r="C37" s="13"/>
+      <c r="D37" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="K37" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M37" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="H37" s="12"/>
-      <c r="I37" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" ht="28.2">
+    </row>
+    <row r="38" spans="2:13" ht="28.2">
       <c r="B38" s="1"/>
-      <c r="C38" s="15"/>
+      <c r="C38" s="1"/>
       <c r="D38" s="15"/>
       <c r="E38" s="15"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J38" s="6" t="s">
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" ht="28.2">
+      <c r="B39" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="39" spans="2:10" ht="28.2">
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="1"/>
+      <c r="D39" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M39" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J39" s="6" t="s">
+    </row>
+    <row r="40" spans="2:13" ht="28.2">
+      <c r="B40" s="1" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="40" spans="2:10" ht="28.2">
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1"/>
+      <c r="D40" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M40" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J40" s="6" t="s">
+    </row>
+    <row r="41" spans="2:13" ht="28.2">
+      <c r="B41" s="11" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="41" spans="2:10" ht="28.2">
-      <c r="B41" s="11" t="s">
+      <c r="C41" s="11"/>
+      <c r="D41" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" ht="28.2">
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M42" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C41" s="7" t="s">
+    </row>
+    <row r="43" spans="2:13" ht="28.2">
+      <c r="B43" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43" s="11"/>
+      <c r="D43" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M43" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J41" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" ht="28.2">
-      <c r="B42" s="1"/>
-      <c r="C42" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J42" s="6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" ht="28.2">
-      <c r="B43" s="11" t="s">
+    </row>
+    <row r="44" spans="2:13" ht="28.2">
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M44" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="C43" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J43" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" ht="28.2">
-      <c r="B44" s="1"/>
-      <c r="C44" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J44" s="6" t="s">
+    </row>
+    <row r="45" spans="2:13" ht="28.2">
+      <c r="B45" s="1" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="45" spans="2:10" ht="28.2">
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1"/>
+      <c r="D45" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M45" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J45" s="6" t="s">
+    </row>
+    <row r="46" spans="2:13" ht="28.2">
+      <c r="B46" s="11" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="46" spans="2:10" ht="28.2">
-      <c r="B46" s="11" t="s">
+      <c r="C46" s="11"/>
+      <c r="D46" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="9"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" ht="28.2">
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M47" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" ht="28.2">
+      <c r="B48" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="C46" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J46" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" ht="28.2">
-      <c r="B47" s="1"/>
-      <c r="C47" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J47" s="6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10" ht="28.2">
-      <c r="B48" s="11" t="s">
+      <c r="C48" s="11"/>
+      <c r="D48" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K48" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C48" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G48" s="8" t="s">
+      <c r="L48" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M48" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="H48" s="8"/>
-      <c r="I48" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J48" s="6" t="s">
+    </row>
+    <row r="49" spans="2:13" ht="28.2">
+      <c r="B49" s="1" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="49" spans="2:10" ht="28.2">
-      <c r="B49" s="1" t="s">
+      <c r="C49" s="1"/>
+      <c r="D49" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M49" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J49" s="6" t="s">
+    </row>
+    <row r="50" spans="2:13" ht="28.2">
+      <c r="B50" s="1" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="50" spans="2:10" ht="28.2">
-      <c r="B50" s="1" t="s">
+      <c r="C50" s="1"/>
+      <c r="D50" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M50" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J50" s="6" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" ht="28.2">
+    </row>
+    <row r="51" spans="2:13" ht="28.2">
       <c r="B51" s="1"/>
-      <c r="C51" s="2"/>
+      <c r="C51" s="1"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
-      <c r="F51" s="3" t="s">
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="K51" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="G51" s="16" t="s">
+      <c r="L51" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M51" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="H51" s="16"/>
-      <c r="I51" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J51" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" ht="28.2">
+    </row>
+    <row r="52" spans="2:13" ht="28.2">
       <c r="B52" s="1"/>
-      <c r="C52" s="15"/>
+      <c r="C52" s="1"/>
       <c r="D52" s="15"/>
       <c r="E52" s="15"/>
-      <c r="F52" s="3" t="s">
+      <c r="F52" s="15"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K52" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="G52" s="16" t="s">
+      <c r="L52" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M52" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="H52" s="16"/>
-      <c r="I52" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J52" s="6" t="s">
+    </row>
+    <row r="53" spans="2:13" ht="28.2">
+      <c r="B53" s="1" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="53" spans="2:10" ht="28.2">
-      <c r="B53" s="1" t="s">
+      <c r="C53" s="1"/>
+      <c r="D53" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M53" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J53" s="6" t="s">
+    </row>
+    <row r="54" spans="2:13" ht="28.2">
+      <c r="B54" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="54" spans="2:10" ht="28.2">
-      <c r="B54" s="1" t="s">
+      <c r="C54" s="1"/>
+      <c r="D54" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M54" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J54" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10" ht="28.2">
+    </row>
+    <row r="55" spans="2:13" ht="28.2">
       <c r="B55" s="1"/>
-      <c r="C55" s="17"/>
+      <c r="C55" s="1"/>
       <c r="D55" s="17"/>
       <c r="E55" s="17"/>
-      <c r="F55" s="3" t="s">
+      <c r="F55" s="17"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="17"/>
+      <c r="I55" s="17"/>
+      <c r="J55" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="K55" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="G55" s="16" t="s">
+      <c r="L55" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="H55" s="16"/>
-      <c r="I55" s="5" t="s">
+      <c r="M55" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="J55" s="18" t="s">
+    </row>
+    <row r="56" spans="2:13" ht="28.2">
+      <c r="B56" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="15"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="15"/>
+      <c r="H56" s="15"/>
+      <c r="I56" s="15"/>
+      <c r="J56" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="56" spans="2:10" ht="28.2">
-      <c r="B56" s="3" t="s">
+      <c r="K56" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="L56" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="M56" s="18" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="57" spans="2:13" ht="28.2">
+      <c r="B57" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C57" s="3"/>
+      <c r="D57" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="E57" s="15"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="15"/>
+      <c r="H57" s="15"/>
+      <c r="I57" s="15"/>
+      <c r="J57" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="L57" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="M57" s="18" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" ht="28.2">
+      <c r="B58" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C58" s="9"/>
+      <c r="D58" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13" ht="28.2">
+      <c r="B59" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C59" s="3"/>
+      <c r="D59" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" ht="28.2">
+      <c r="B60" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C60" s="9"/>
+      <c r="D60" s="12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13" ht="28.2">
+      <c r="B61" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C56" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D56" s="15"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="3" t="s">
+    </row>
+    <row r="62" spans="2:13" ht="28.2">
+      <c r="B62" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C62" s="14"/>
+      <c r="D62" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" ht="28.2">
+      <c r="B63" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C63" s="3"/>
+      <c r="D63" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" ht="28.2">
+      <c r="B64" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C64" s="3"/>
+      <c r="D64" s="16" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" ht="28.2">
+      <c r="B65" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C65" s="3"/>
+      <c r="D65" s="16" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" ht="28.2">
+      <c r="B66" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C66" s="3"/>
+      <c r="D66" s="16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" ht="28.2">
+      <c r="B67" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C67" s="3"/>
+      <c r="D67" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="G56" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="H56" s="16"/>
-      <c r="I56" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="J56" s="18" t="s">
+    </row>
+    <row r="68" spans="2:4" ht="28.2">
+      <c r="B68" s="3" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="57" spans="2:10" ht="28.2">
-      <c r="B57" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C57" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="G57" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="H57" s="16"/>
-      <c r="I57" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="J57" s="18" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10" ht="28.2">
-      <c r="B58" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10" ht="28.2">
-      <c r="B59" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10" ht="28.2">
-      <c r="B60" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C60" s="12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10" ht="28.2">
-      <c r="B61" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10" ht="28.2">
-      <c r="B62" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="63" spans="2:10" ht="28.2">
-      <c r="B63" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10" ht="28.2">
-      <c r="B64" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" ht="28.2">
-      <c r="B65" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C65" s="16" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" ht="28.2">
-      <c r="B66" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C66" s="16" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="67" spans="2:3" ht="28.2">
-      <c r="B67" s="3" t="s">
+      <c r="C68" s="3"/>
+      <c r="D68" s="16" t="s">
         <v>156</v>
-      </c>
-      <c r="C67" s="16" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="68" spans="2:3" ht="28.2">
-      <c r="B68" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C68" s="16" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset/Alphabets-Dataset/burushaski-characters.xlsx
+++ b/Dataset/Alphabets-Dataset/burushaski-characters.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="279">
   <si>
     <t>Unicode</t>
   </si>
@@ -371,9 +371,6 @@
     <t>U+ ‎0654</t>
   </si>
   <si>
-    <t>HAMZA ABOVE</t>
-  </si>
-  <si>
     <t>ہ</t>
   </si>
   <si>
@@ -540,13 +537,337 @@
   </si>
   <si>
     <t>flower</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>ب</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>ts</t>
+  </si>
+  <si>
+    <t>kh</t>
+  </si>
+  <si>
+    <t>ā</t>
+  </si>
+  <si>
+    <t>āa</t>
+  </si>
+  <si>
+    <t>/ɑː/</t>
+  </si>
+  <si>
+    <t>ṭ</t>
+  </si>
+  <si>
+    <t>ch</t>
+  </si>
+  <si>
+    <t>ḍ</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>dz</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>r°</t>
+  </si>
+  <si>
+    <t>ṛ</t>
+  </si>
+  <si>
+    <t>zh</t>
+  </si>
+  <si>
+    <t>sh</t>
+  </si>
+  <si>
+    <t>gh</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>l̥</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>ń</t>
+  </si>
+  <si>
+    <t>w / u</t>
+  </si>
+  <si>
+    <t>o / oo</t>
+  </si>
+  <si>
+    <t>o / u̯</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>y / i</t>
+  </si>
+  <si>
+    <t>ii / ī</t>
+  </si>
+  <si>
+    <t>ll</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>ee</t>
+  </si>
+  <si>
+    <t>ẏ</t>
+  </si>
+  <si>
+    <t>ė</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>ṣ</t>
+  </si>
+  <si>
+    <t>ع</t>
+  </si>
+  <si>
+    <t>ف</t>
+  </si>
+  <si>
+    <t>pʰ</t>
+  </si>
+  <si>
+    <t>U+0641</t>
+  </si>
+  <si>
+    <t>U+0639</t>
+  </si>
+  <si>
+    <t>ث</t>
+  </si>
+  <si>
+    <t>U+062B</t>
+  </si>
+  <si>
+    <t>062B</t>
+  </si>
+  <si>
+    <t>/s/</t>
+  </si>
+  <si>
+    <t>‎0627</t>
+  </si>
+  <si>
+    <t>‎062A</t>
+  </si>
+  <si>
+    <t>‎0679</t>
+  </si>
+  <si>
+    <t>‎062C</t>
+  </si>
+  <si>
+    <t>‎0686</t>
+  </si>
+  <si>
+    <t>‎0685</t>
+  </si>
+  <si>
+    <t>‎062E</t>
+  </si>
+  <si>
+    <t>‎062F</t>
+  </si>
+  <si>
+    <t>‎0688</t>
+  </si>
+  <si>
+    <t>‎0630</t>
+  </si>
+  <si>
+    <t>ح</t>
+  </si>
+  <si>
+    <t>U+062D</t>
+  </si>
+  <si>
+    <t>ḥ</t>
+  </si>
+  <si>
+    <t>/ħ/</t>
+  </si>
+  <si>
+    <t>ص</t>
+  </si>
+  <si>
+    <t>ض</t>
+  </si>
+  <si>
+    <t>U+0636</t>
+  </si>
+  <si>
+    <t>U+0635</t>
+  </si>
+  <si>
+    <t>s̱</t>
+  </si>
+  <si>
+    <t>ẓ</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>067E</t>
+  </si>
+  <si>
+    <t>062D</t>
+  </si>
+  <si>
+    <t>‎068E</t>
+  </si>
+  <si>
+    <t>‎0631</t>
+  </si>
+  <si>
+    <t>‎0691</t>
+  </si>
+  <si>
+    <t>‎0632</t>
+  </si>
+  <si>
+    <t>‎0698</t>
+  </si>
+  <si>
+    <t>‎0633</t>
+  </si>
+  <si>
+    <t>‎0634</t>
+  </si>
+  <si>
+    <t>‎075C</t>
+  </si>
+  <si>
+    <t>‎063A</t>
+  </si>
+  <si>
+    <t>‎0644</t>
+  </si>
+  <si>
+    <t>‎0645</t>
+  </si>
+  <si>
+    <t>‎0646</t>
+  </si>
+  <si>
+    <t>06A9</t>
+  </si>
+  <si>
+    <t>06AF</t>
+  </si>
+  <si>
+    <t>‎0648</t>
+  </si>
+  <si>
+    <t>‎06C1</t>
+  </si>
+  <si>
+    <t>‎06CC</t>
+  </si>
+  <si>
+    <t>06CC</t>
+  </si>
+  <si>
+    <t>‎08F7</t>
+  </si>
+  <si>
+    <t>‎065A</t>
+  </si>
+  <si>
+    <t>‎06D2</t>
+  </si>
+  <si>
+    <t>002E</t>
+  </si>
+  <si>
+    <t>061F</t>
+  </si>
+  <si>
+    <t>060C</t>
+  </si>
+  <si>
+    <t>‎0652</t>
+  </si>
+  <si>
+    <t>‎065</t>
+  </si>
+  <si>
+    <t>‎0654</t>
+  </si>
+  <si>
+    <t>‎0670</t>
+  </si>
+  <si>
+    <t>08F7</t>
+  </si>
+  <si>
+    <t>064E</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="14">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -633,6 +954,41 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="22"/>
+      <color rgb="FF000000"/>
+      <name val="Scheherazade New"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color rgb="FF000000"/>
+      <name val="Scheherazade New"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Nastaliq Urdu"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -678,11 +1034,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -710,14 +1063,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -741,6 +1088,69 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1023,1423 +1433,1774 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
-    <col min="2" max="3" width="20.109375" customWidth="1"/>
-    <col min="4" max="9" width="29.109375" customWidth="1"/>
+    <col min="2" max="3" width="20.109375" style="20" customWidth="1"/>
+    <col min="4" max="4" width="29.109375" style="26" customWidth="1"/>
+    <col min="5" max="5" width="29.109375" style="20" customWidth="1"/>
+    <col min="6" max="9" width="29.109375" customWidth="1"/>
     <col min="10" max="10" width="27" customWidth="1"/>
     <col min="11" max="11" width="27.88671875" customWidth="1"/>
     <col min="12" max="12" width="28.44140625" customWidth="1"/>
     <col min="13" max="13" width="49.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="20" customFormat="1" ht="15.6">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:13" s="17" customFormat="1" ht="15.6">
+      <c r="A1" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="J1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="28.2">
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1">
+        <v>627</v>
+      </c>
+      <c r="F2" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="F1" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="G1" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="H1" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="I1" s="21" t="s">
+      <c r="G2" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="J1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="M1" s="21" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="28.2">
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="2" t="s">
+      <c r="H2" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="28.2">
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="2">
-        <v>627</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="I2" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="28.2">
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="3" t="s">
+      <c r="E3" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M3" s="6" t="s">
+      <c r="L3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="28.2">
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="2" t="s">
+      <c r="C4" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="D4" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M4" s="6" t="s">
+      <c r="E4" s="1">
+        <v>622</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="28.2">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>173</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="1">
+        <v>628</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="28.2">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="28.2">
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="2" t="s">
+      <c r="C6" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M6" s="6" t="s">
+      <c r="E6" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M6" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="28.2">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="2" t="s">
+      <c r="C7" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M7" s="6" t="s">
+      <c r="E7" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M7" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="28.2">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="2" t="s">
+      <c r="C8" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M8" s="6" t="s">
+      <c r="E8" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M8" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="28.2">
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="5"/>
+    </row>
+    <row r="10" spans="1:13" ht="28.2">
+      <c r="B10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="2" t="s">
+      <c r="C10" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M9" s="6" t="s">
+      <c r="E10" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M10" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="28.2">
-      <c r="B10" s="1" t="s">
+    <row r="11" spans="1:13" ht="28.2">
+      <c r="B11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2" t="s">
+      <c r="C11" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="D11" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M10" s="6" t="s">
+      <c r="E11" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M11" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="28.2">
-      <c r="B11" s="1" t="s">
+    <row r="12" spans="1:13" ht="28.2">
+      <c r="B12" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="5"/>
+    </row>
+    <row r="13" spans="1:13" ht="28.2">
+      <c r="B13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="2" t="s">
+      <c r="C13" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="D13" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="5" t="s">
+      <c r="E13" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="M13" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="28.2">
-      <c r="B12" s="1" t="s">
+    <row r="14" spans="1:13" ht="28.2">
+      <c r="B14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="2" t="s">
+      <c r="C14" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="D14" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M12" s="6" t="s">
+      <c r="E14" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M14" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="28.2">
-      <c r="B13" s="1" t="s">
+    <row r="15" spans="1:13" ht="28.2">
+      <c r="B15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="2" t="s">
+      <c r="C15" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="D15" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M13" s="6" t="s">
+      <c r="E15" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M15" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="28.2">
-      <c r="B14" s="1" t="s">
+    <row r="16" spans="1:13" ht="28.2">
+      <c r="B16" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2" t="s">
+      <c r="C16" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M14" s="6" t="s">
+      <c r="E16" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M16" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="28.2">
-      <c r="B15" s="1" t="s">
+    <row r="17" spans="2:13" ht="28.2">
+      <c r="B17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="2" t="s">
+      <c r="C17" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="D17" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M15" s="6" t="s">
+      <c r="E17" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M17" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="28.2">
-      <c r="B16" s="1" t="s">
+    <row r="18" spans="2:13" ht="28.2">
+      <c r="B18" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="2" t="s">
+      <c r="C18" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="D18" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M16" s="6" t="s">
+      <c r="E18" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M18" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="2:13" ht="28.2">
-      <c r="B17" s="1" t="s">
+    <row r="19" spans="2:13" ht="28.2">
+      <c r="B19" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="2" t="s">
+      <c r="C19" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="D19" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M17" s="6" t="s">
+      <c r="E19" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M19" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="2:13" ht="28.2">
-      <c r="B18" s="1" t="s">
+    <row r="20" spans="2:13" ht="28.2">
+      <c r="B20" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="7" t="s">
+      <c r="C20" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="D20" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="3" t="s">
+      <c r="E20" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="K20" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="L18" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M18" s="6" t="s">
+      <c r="L20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M20" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="2:13" ht="28.2">
-      <c r="B19" s="1" t="s">
+    <row r="21" spans="2:13" ht="28.2">
+      <c r="B21" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="2" t="s">
+      <c r="C21" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="D21" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M19" s="6" t="s">
+      <c r="E21" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M21" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="2:13" ht="28.2">
-      <c r="B20" s="1" t="s">
+    <row r="22" spans="2:13" ht="28.2">
+      <c r="B22" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="7" t="s">
+      <c r="C22" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="D22" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M20" s="6" t="s">
+      <c r="E22" s="28" t="s">
+        <v>252</v>
+      </c>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M22" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="2:13" ht="28.2">
-      <c r="B21" s="1" t="s">
+    <row r="23" spans="2:13" ht="28.2">
+      <c r="B23" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="7" t="s">
+      <c r="C23" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="D23" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M21" s="6" t="s">
+      <c r="E23" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M23" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="2:13" ht="28.2">
-      <c r="B22" s="1" t="s">
+    <row r="24" spans="2:13" ht="28.2">
+      <c r="B24" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="2" t="s">
+      <c r="C24" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="D24" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M22" s="6" t="s">
+      <c r="E24" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M24" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="2:13" ht="28.2">
-      <c r="B23" s="1" t="s">
+    <row r="25" spans="2:13" ht="28.2">
+      <c r="B25" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="2" t="s">
+      <c r="C25" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D25" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M23" s="6" t="s">
+      <c r="E25" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M25" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="2:13" ht="28.2">
-      <c r="B24" s="1" t="s">
+    <row r="26" spans="2:13" ht="28.2">
+      <c r="B26" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="2" t="s">
+      <c r="C26" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="D26" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="5" t="s">
+      <c r="E26" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="M24" s="6" t="s">
+      <c r="M26" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="2:13" ht="28.2">
-      <c r="B25" s="1" t="s">
+    <row r="27" spans="2:13" ht="28.2">
+      <c r="B27" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="E27" s="1">
+        <v>635</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="5"/>
+    </row>
+    <row r="28" spans="2:13" ht="28.2">
+      <c r="B28" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="E28" s="1">
+        <v>636</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="5"/>
+    </row>
+    <row r="29" spans="2:13" ht="28.2">
+      <c r="B29" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="E29" s="1">
+        <v>639</v>
+      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="5"/>
+    </row>
+    <row r="30" spans="2:13" ht="28.2">
+      <c r="B30" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="2" t="s">
+      <c r="C30" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="D30" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M25" s="6" t="s">
+      <c r="E30" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M30" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="2:13" ht="28.2">
-      <c r="B26" s="1" t="s">
+    <row r="31" spans="2:13" ht="28.2">
+      <c r="B31" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="E31" s="1">
+        <v>641</v>
+      </c>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="5"/>
+    </row>
+    <row r="32" spans="2:13" ht="28.2">
+      <c r="B32" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="2" t="s">
+      <c r="C32" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="D32" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M26" s="6" t="s">
+      <c r="E32" s="1">
+        <v>642</v>
+      </c>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M32" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="2:13" ht="28.2">
-      <c r="B27" s="1" t="s">
+    <row r="33" spans="2:13" ht="28.2">
+      <c r="B33" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="2" t="s">
+      <c r="C33" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="D33" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M27" s="6" t="s">
+      <c r="E33" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M33" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="28.2">
-      <c r="B28" s="1" t="s">
+    <row r="34" spans="2:13" ht="28.2">
+      <c r="B34" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="2" t="s">
+      <c r="C34" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M28" s="6" t="s">
+      <c r="E34" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M34" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="2:13" ht="28.2">
-      <c r="B29" s="1" t="s">
+    <row r="35" spans="2:13" ht="28.2">
+      <c r="B35" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="2" t="s">
+      <c r="C35" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="D35" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M29" s="6" t="s">
+      <c r="E35" s="1">
+        <v>644</v>
+      </c>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M35" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="30" spans="2:13" ht="28.2">
-      <c r="B30" s="11" t="s">
+    <row r="36" spans="2:13" ht="28.2">
+      <c r="B36" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="7" t="s">
+      <c r="C36" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="D36" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="9" t="s">
+      <c r="E36" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="K30" s="8" t="s">
+      <c r="K36" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="L30" s="5" t="s">
+      <c r="L36" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="M30" s="6" t="s">
+      <c r="M36" s="5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="2:13" ht="28.2">
-      <c r="B31" s="11" t="s">
+    <row r="37" spans="2:13" ht="28.2">
+      <c r="B37" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="7" t="s">
+      <c r="C37" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="D37" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="3" t="s">
+      <c r="E37" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K31" s="8" t="s">
+      <c r="K37" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="L31" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M31" s="6" t="s">
+      <c r="L37" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M37" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="32" spans="2:13" ht="28.2">
-      <c r="B32" s="1" t="s">
+    <row r="38" spans="2:13" ht="28.2">
+      <c r="B38" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="1"/>
-      <c r="D32" s="2" t="s">
+      <c r="C38" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="D38" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M32" s="6" t="s">
+      <c r="E38" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M38" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="33" spans="2:13" ht="28.2">
-      <c r="B33" s="1" t="s">
+    <row r="39" spans="2:13" ht="28.2">
+      <c r="B39" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="2" t="s">
+      <c r="C39" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D39" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M33" s="6" t="s">
+      <c r="E39" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M39" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="28.2">
-      <c r="B34" s="11" t="s">
+    <row r="40" spans="2:13" ht="28.2">
+      <c r="B40" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C34" s="11"/>
-      <c r="D34" s="7" t="s">
+      <c r="C40" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="D40" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="9" t="s">
+      <c r="E40" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="K34" s="12" t="s">
+      <c r="K40" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="L34" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M34" s="6" t="s">
+      <c r="L40" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M40" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="35" spans="2:13" ht="28.2">
-      <c r="B35" s="1" t="s">
+    <row r="41" spans="2:13" ht="28.2">
+      <c r="B41" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="2" t="s">
+      <c r="C41" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="D41" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M35" s="6" t="s">
+      <c r="E41" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M41" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="36" spans="2:13" ht="28.2">
-      <c r="B36" s="11" t="s">
+    <row r="42" spans="2:13" ht="28.2">
+      <c r="B42" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C36" s="11"/>
-      <c r="D36" s="7" t="s">
+      <c r="C42" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="D42" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="3" t="s">
+      <c r="E42" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K36" s="12" t="s">
+      <c r="K42" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="L36" s="5" t="s">
+      <c r="L42" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="M36" s="6" t="s">
+      <c r="M42" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="28.2">
-      <c r="B37" s="13" t="s">
+    <row r="43" spans="2:13" ht="28.2">
+      <c r="B43" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="7" t="s">
+      <c r="C43" s="39" t="s">
+        <v>205</v>
+      </c>
+      <c r="D43" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="14" t="s">
+      <c r="E43" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="K37" s="12" t="s">
+      <c r="K43" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="L37" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M37" s="6" t="s">
+      <c r="L43" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M43" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="28.2">
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M38" s="6" t="s">
+    <row r="44" spans="2:13" ht="28.2">
+      <c r="B44" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" ht="28.2">
-      <c r="B39" s="1" t="s">
+      <c r="C44" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="D44" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="2" t="s">
+      <c r="E44" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M44" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M39" s="6" t="s">
+    </row>
+    <row r="45" spans="2:13" ht="28.2">
+      <c r="B45" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="40" spans="2:13" ht="28.2">
-      <c r="B40" s="1" t="s">
+      <c r="C45" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="D45" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="C40" s="1"/>
-      <c r="D40" s="2" t="s">
+      <c r="E45" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M45" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M40" s="6" t="s">
+    </row>
+    <row r="46" spans="2:13" ht="28.2">
+      <c r="B46" s="8" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="41" spans="2:13" ht="28.2">
-      <c r="B41" s="11" t="s">
+      <c r="C46" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="D46" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="E46" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M46" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" ht="28.2">
+      <c r="B47" s="2"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="28" t="s">
+        <v>267</v>
+      </c>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M47" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C41" s="11"/>
-      <c r="D41" s="7" t="s">
+    </row>
+    <row r="48" spans="2:13" ht="28.2">
+      <c r="B48" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="D48" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="E48" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M48" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="9"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M41" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="42" spans="2:13" ht="28.2">
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="7" t="s">
+    </row>
+    <row r="49" spans="2:13" ht="28.2">
+      <c r="B49" s="2"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="E49" s="28" t="s">
+        <v>268</v>
+      </c>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M49" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13" ht="28.2">
+      <c r="B50" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="D50" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M50" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13" ht="28.2">
+      <c r="B51" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="D51" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="E51" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M51" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" ht="28.2">
+      <c r="B52" s="2"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M42" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="43" spans="2:13" ht="28.2">
-      <c r="B43" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="C43" s="11"/>
-      <c r="D43" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="9"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M43" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="44" spans="2:13" ht="28.2">
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="7" t="s">
+      <c r="E52" s="28" t="s">
+        <v>267</v>
+      </c>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="9"/>
+      <c r="L52" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M52" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13" ht="28.2">
+      <c r="B53" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C53" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="D53" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="E53" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M53" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54" spans="2:13" ht="28.2">
+      <c r="B54" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="D54" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M54" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13" ht="28.2">
+      <c r="B55" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C55" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="D55" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="E55" s="28" t="s">
+        <v>271</v>
+      </c>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="9"/>
+      <c r="L55" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M55" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13" ht="28.2">
+      <c r="B56" s="2"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K56" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="L56" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M56" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="57" spans="2:13" ht="28.2">
+      <c r="B57" s="2"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="33"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+      <c r="I57" s="12"/>
+      <c r="J57" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="K57" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M57" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" ht="28.2">
+      <c r="B58" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C58" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="D58" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="E58" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="3"/>
+      <c r="L58" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M58" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13" ht="28.2">
+      <c r="B59" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C59" s="21"/>
+      <c r="D59" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="E59" s="1">
+        <v>614</v>
+      </c>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="3"/>
+      <c r="L59" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M59" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" ht="28.2">
+      <c r="B60" s="2"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K60" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="M60" s="15" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13" ht="28.2">
+      <c r="B61" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="21"/>
+      <c r="D61" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" s="31" t="s">
+        <v>267</v>
+      </c>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+      <c r="I61" s="12"/>
+      <c r="J61" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="K61" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="M61" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13" ht="28.2">
+      <c r="B62" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C62" s="21"/>
+      <c r="D62" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="E62" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
+      <c r="J62" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="K62" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="M62" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" ht="28.2">
+      <c r="B63" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="9"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M44" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="45" spans="2:13" ht="28.2">
-      <c r="B45" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C45" s="1"/>
-      <c r="D45" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="4"/>
-      <c r="L45" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M45" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="46" spans="2:13" ht="28.2">
-      <c r="B46" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C46" s="11"/>
-      <c r="D46" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="9"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M46" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="47" spans="2:13" ht="28.2">
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="7" t="s">
+      <c r="E63" s="20" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" ht="28.2">
+      <c r="B64" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C64" s="21"/>
+      <c r="D64" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" ht="28.2">
+      <c r="B65" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C65" s="22"/>
+      <c r="D65" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" ht="28.2">
+      <c r="B66" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="21"/>
+      <c r="D66" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="9"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M47" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="48" spans="2:13" ht="28.2">
-      <c r="B48" s="11" t="s">
+      <c r="E66" s="20" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" ht="28.2">
+      <c r="B67" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C67" s="23"/>
+      <c r="D67" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="E67" s="20" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" ht="28.2">
+      <c r="B68" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C68" s="21"/>
+      <c r="D68" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="C48" s="11"/>
-      <c r="D48" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="K48" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="L48" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M48" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="49" spans="2:13" ht="28.2">
-      <c r="B49" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C49" s="1"/>
-      <c r="D49" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M49" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="50" spans="2:13" ht="28.2">
-      <c r="B50" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C50" s="1"/>
-      <c r="D50" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M50" s="6" t="s">
+      <c r="E68" s="20" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" ht="28.2">
+      <c r="B69" s="2" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="51" spans="2:13" ht="28.2">
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="3" t="s">
+      <c r="C69" s="21"/>
+      <c r="D69" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="K51" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="L51" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M51" s="6" t="s">
+      <c r="E69" s="20" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" ht="28.2">
+      <c r="B70" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="52" spans="2:13" ht="28.2">
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="15"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="3" t="s">
+      <c r="C70" s="21"/>
+      <c r="D70" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="K52" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="L52" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M52" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="53" spans="2:13" ht="28.2">
-      <c r="B53" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C53" s="1"/>
-      <c r="D53" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M53" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="54" spans="2:13" ht="28.2">
-      <c r="B54" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C54" s="1"/>
-      <c r="D54" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="3"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M54" s="6" t="s">
+      <c r="E70" s="20">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5" ht="28.2">
+      <c r="B71" s="2" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="55" spans="2:13" ht="28.2">
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="17"/>
-      <c r="G55" s="17"/>
-      <c r="H55" s="17"/>
-      <c r="I55" s="17"/>
-      <c r="J55" s="3" t="s">
+      <c r="C71" s="21"/>
+      <c r="D71" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="K55" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="L55" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="M55" s="18" t="s">
+      <c r="E71" s="20" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" ht="28.2">
+      <c r="B72" s="2" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="56" spans="2:13" ht="28.2">
-      <c r="B56" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" s="3"/>
-      <c r="D56" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="15"/>
-      <c r="I56" s="15"/>
-      <c r="J56" s="3" t="s">
+      <c r="C72" s="21"/>
+      <c r="D72" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="K56" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="L56" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="M56" s="18" t="s">
+      <c r="E72" s="20">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" ht="28.2">
+      <c r="B73" s="2" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="57" spans="2:13" ht="28.2">
-      <c r="B57" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C57" s="3"/>
-      <c r="D57" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="15"/>
-      <c r="I57" s="15"/>
-      <c r="J57" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="K57" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="L57" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="M57" s="18" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="58" spans="2:13" ht="28.2">
-      <c r="B58" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C58" s="9"/>
-      <c r="D58" s="8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="59" spans="2:13" ht="28.2">
-      <c r="B59" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C59" s="3"/>
-      <c r="D59" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="60" spans="2:13" ht="28.2">
-      <c r="B60" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C60" s="9"/>
-      <c r="D60" s="12" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="61" spans="2:13" ht="28.2">
-      <c r="B61" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" s="3"/>
-      <c r="D61" s="12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="2:13" ht="28.2">
-      <c r="B62" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="C62" s="14"/>
-      <c r="D62" s="12" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="63" spans="2:13" ht="28.2">
-      <c r="B63" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C63" s="3"/>
-      <c r="D63" s="8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="64" spans="2:13" ht="28.2">
-      <c r="B64" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C64" s="3"/>
-      <c r="D64" s="16" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4" ht="28.2">
-      <c r="B65" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C65" s="3"/>
-      <c r="D65" s="16" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4" ht="28.2">
-      <c r="B66" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C66" s="3"/>
-      <c r="D66" s="16" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4" ht="28.2">
-      <c r="B67" s="3" t="s">
+      <c r="C73" s="21"/>
+      <c r="D73" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="C67" s="3"/>
-      <c r="D67" s="16" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4" ht="28.2">
-      <c r="B68" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C68" s="3"/>
-      <c r="D68" s="16" t="s">
-        <v>156</v>
+      <c r="E73" s="20">
+        <v>650</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset/Alphabets-Dataset/burushaski-characters.xlsx
+++ b/Dataset/Alphabets-Dataset/burushaski-characters.xlsx
@@ -13,6 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="filtered" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="369">
   <si>
     <t>Unicode</t>
   </si>
@@ -68,9 +69,6 @@
     <t>آ</t>
   </si>
   <si>
-    <t>U+ ‎0622</t>
-  </si>
-  <si>
     <t>LETTER ALEF WITH MADD A ABOVE</t>
   </si>
   <si>
@@ -533,9 +531,6 @@
     <t>اسقور</t>
   </si>
   <si>
-    <t>aasqor</t>
-  </si>
-  <si>
     <t>flower</t>
   </si>
   <si>
@@ -572,9 +567,6 @@
     <t>ā</t>
   </si>
   <si>
-    <t>āa</t>
-  </si>
-  <si>
     <t>/ɑː/</t>
   </si>
   <si>
@@ -704,7 +696,7 @@
     <t>/s/</t>
   </si>
   <si>
-    <t>‎0627</t>
+    <t>/z/</t>
   </si>
   <si>
     <t>‎062A</t>
@@ -861,13 +853,292 @@
   </si>
   <si>
     <t>064E</t>
+  </si>
+  <si>
+    <t>ã</t>
+  </si>
+  <si>
+    <t>U+0101</t>
+  </si>
+  <si>
+    <t>U+00E3</t>
+  </si>
+  <si>
+    <t>/ã/</t>
+  </si>
+  <si>
+    <t>/b/</t>
+  </si>
+  <si>
+    <t>/p/</t>
+  </si>
+  <si>
+    <t>/t̪/</t>
+  </si>
+  <si>
+    <t>/ʈ/</t>
+  </si>
+  <si>
+    <t>/d͡ʒ/</t>
+  </si>
+  <si>
+    <t>/t͡ʃ/</t>
+  </si>
+  <si>
+    <t>/t͡s/</t>
+  </si>
+  <si>
+    <t>/x/</t>
+  </si>
+  <si>
+    <t>/d̪/</t>
+  </si>
+  <si>
+    <t>/ɖ/</t>
+  </si>
+  <si>
+    <t>/d͡z/</t>
+  </si>
+  <si>
+    <t>/r/</t>
+  </si>
+  <si>
+    <t>/ɾ̊/</t>
+  </si>
+  <si>
+    <t>/ɽ/</t>
+  </si>
+  <si>
+    <t>/ʒ/</t>
+  </si>
+  <si>
+    <t>/ʃ/</t>
+  </si>
+  <si>
+    <t>/ʂ/</t>
+  </si>
+  <si>
+    <t>/sː/</t>
+  </si>
+  <si>
+    <t>/zˤ/</t>
+  </si>
+  <si>
+    <t>/e/</t>
+  </si>
+  <si>
+    <t>/ɣ/</t>
+  </si>
+  <si>
+    <t>/pʰ/</t>
+  </si>
+  <si>
+    <t>/q/</t>
+  </si>
+  <si>
+    <t>/k/</t>
+  </si>
+  <si>
+    <t>/ɡ/</t>
+  </si>
+  <si>
+    <t>/l/</t>
+  </si>
+  <si>
+    <t>/lː/</t>
+  </si>
+  <si>
+    <t>/l̥/</t>
+  </si>
+  <si>
+    <t>/m/</t>
+  </si>
+  <si>
+    <t>/n/</t>
+  </si>
+  <si>
+    <t>/ɲ/</t>
+  </si>
+  <si>
+    <t>/w/ ~ /u/</t>
+  </si>
+  <si>
+    <t>/o/ ~ /oː/</t>
+  </si>
+  <si>
+    <t>/o̯/</t>
+  </si>
+  <si>
+    <t>/h/</t>
+  </si>
+  <si>
+    <t>/j/ ~ /i/</t>
+  </si>
+  <si>
+    <t>/iː/</t>
+  </si>
+  <si>
+    <t>/ʝ/ or /j̝/</t>
+  </si>
+  <si>
+    <t>/eː/</t>
+  </si>
+  <si>
+    <t>/ə/</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>/ʔ/</t>
+  </si>
+  <si>
+    <t>asqor</t>
+  </si>
+  <si>
+    <t>سان</t>
+  </si>
+  <si>
+    <t>بُش</t>
+  </si>
+  <si>
+    <t>پھوࣷپوࣷس</t>
+  </si>
+  <si>
+    <t>تلٚ</t>
+  </si>
+  <si>
+    <t>ٹوری</t>
+  </si>
+  <si>
+    <t>جالو</t>
+  </si>
+  <si>
+    <t>چقر</t>
+  </si>
+  <si>
+    <t>څُخ</t>
+  </si>
+  <si>
+    <t>خوࣷروࣷنٚ</t>
+  </si>
+  <si>
+    <t>داسیࣷن</t>
+  </si>
+  <si>
+    <t>ڈَڈنٚ</t>
+  </si>
+  <si>
+    <t>ڎَپیࣷ</t>
+  </si>
+  <si>
+    <t>ہَر</t>
+  </si>
+  <si>
+    <t>ڈر</t>
+  </si>
+  <si>
+    <t>زوئی</t>
+  </si>
+  <si>
+    <t>ژکُن</t>
+  </si>
+  <si>
+    <t>ساࣷ</t>
+  </si>
+  <si>
+    <t>شےࣷ</t>
+  </si>
+  <si>
+    <t>ݜَر</t>
+  </si>
+  <si>
+    <t>ط</t>
+  </si>
+  <si>
+    <t>ظ</t>
+  </si>
+  <si>
+    <t>/tˤ/</t>
+  </si>
+  <si>
+    <t>U+0637</t>
+  </si>
+  <si>
+    <t>U+0638</t>
+  </si>
+  <si>
+    <t>غئیِنٚ</t>
+  </si>
+  <si>
+    <t>قرقَمُش</t>
+  </si>
+  <si>
+    <t>کُکُریࣷس</t>
+  </si>
+  <si>
+    <t>گِری</t>
+  </si>
+  <si>
+    <t>لاجِک</t>
+  </si>
+  <si>
+    <t>لٚمن</t>
+  </si>
+  <si>
+    <t>ممُو</t>
+  </si>
+  <si>
+    <t>نَروࣷ</t>
+  </si>
+  <si>
+    <t>ہِنٚ</t>
+  </si>
+  <si>
+    <t>وَٹ</t>
+  </si>
+  <si>
+    <t>ہغوࣷر</t>
+  </si>
+  <si>
+    <t>یٹھل</t>
+  </si>
+  <si>
+    <t>لایࣷ</t>
+  </si>
+  <si>
+    <t>sā</t>
+  </si>
+  <si>
+    <t>sun</t>
+  </si>
+  <si>
+    <t>E3</t>
+  </si>
+  <si>
+    <t>سآن ساࣷن</t>
+  </si>
+  <si>
+    <t>sãnsān</t>
+  </si>
+  <si>
+    <t>some days before</t>
+  </si>
+  <si>
+    <t>bush</t>
+  </si>
+  <si>
+    <t>cat</t>
+  </si>
+  <si>
+    <t>Burushaski Script (Nastaliq &amp; Roman)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -989,6 +1260,16 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="11"/>
+      <color theme="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1034,7 +1315,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1105,14 +1386,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1153,6 +1452,19 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="11" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1433,14 +1745,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
     <col min="2" max="3" width="20.109375" style="20" customWidth="1"/>
-    <col min="4" max="4" width="29.109375" style="26" customWidth="1"/>
+    <col min="4" max="4" width="29.109375" style="29" customWidth="1"/>
     <col min="5" max="5" width="29.109375" style="20" customWidth="1"/>
-    <col min="6" max="9" width="29.109375" customWidth="1"/>
+    <col min="6" max="6" width="29.109375" customWidth="1"/>
+    <col min="7" max="8" width="29.109375" style="20" customWidth="1"/>
+    <col min="9" max="9" width="29.109375" style="27" customWidth="1"/>
     <col min="10" max="10" width="27" customWidth="1"/>
     <col min="11" max="11" width="27.88671875" customWidth="1"/>
     <col min="12" max="12" width="28.44140625" customWidth="1"/>
@@ -1449,31 +1763,31 @@
   <sheetData>
     <row r="1" spans="1:13" s="17" customFormat="1" ht="15.6">
       <c r="A1" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="B1" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="C1" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="30" t="s">
         <v>163</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>162</v>
       </c>
       <c r="D1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="F1" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="I1" s="34" t="s">
         <v>166</v>
-      </c>
-      <c r="I1" s="18" t="s">
-        <v>167</v>
       </c>
       <c r="J1" s="18" t="s">
         <v>1</v>
@@ -1492,8 +1806,8 @@
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="38" t="s">
-        <v>171</v>
+      <c r="C2" s="44" t="s">
+        <v>169</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>6</v>
@@ -1502,16 +1816,16 @@
         <v>627</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G2" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="I2" s="26" t="s">
         <v>168</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>170</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="3"/>
@@ -1526,17 +1840,26 @@
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="D3" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>226</v>
+      <c r="C3" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>277</v>
+      </c>
+      <c r="E3" s="20">
+        <v>101</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>183</v>
+        <v>180</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="I3" s="27" t="s">
+        <v>361</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>10</v>
@@ -1555,151 +1878,169 @@
       <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="1">
-        <v>622</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="C4" s="44" t="s">
+        <v>276</v>
+      </c>
+      <c r="D4" s="48" t="s">
+        <v>278</v>
+      </c>
+      <c r="E4" s="49"/>
+      <c r="F4" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>323</v>
+      </c>
       <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+      <c r="I4" s="28"/>
       <c r="J4" s="2"/>
       <c r="K4" s="3"/>
       <c r="L4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="28.2">
       <c r="B5" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>173</v>
+        <v>170</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>171</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1">
         <v>628</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="F5" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>324</v>
+      </c>
       <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
+      <c r="I5" s="28"/>
       <c r="J5" s="2"/>
       <c r="K5" s="3"/>
       <c r="L5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="28.2">
       <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>174</v>
+        <v>15</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>172</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+        <v>244</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>325</v>
+      </c>
       <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+      <c r="I6" s="28"/>
       <c r="J6" s="2"/>
       <c r="K6" s="3"/>
       <c r="L6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="28.2">
       <c r="B7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D7" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>22</v>
-      </c>
       <c r="E7" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+        <v>224</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>326</v>
+      </c>
       <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="I7" s="28"/>
       <c r="J7" s="2"/>
       <c r="K7" s="3"/>
       <c r="L7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="28.2">
       <c r="B8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="D8" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>25</v>
-      </c>
       <c r="E8" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+        <v>225</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>327</v>
+      </c>
       <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+      <c r="I8" s="28"/>
       <c r="J8" s="2"/>
       <c r="K8" s="3"/>
       <c r="L8" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="28.2">
       <c r="B9" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="F9" s="19" t="s">
         <v>222</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>225</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+      <c r="I9" s="28"/>
       <c r="J9" s="2"/>
       <c r="K9" s="3"/>
       <c r="L9" s="4"/>
@@ -1707,75 +2048,83 @@
     </row>
     <row r="10" spans="1:13" ht="28.2">
       <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="D10" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>28</v>
-      </c>
       <c r="E10" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+        <v>226</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>328</v>
+      </c>
       <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+      <c r="I10" s="28"/>
       <c r="J10" s="2"/>
       <c r="K10" s="3"/>
       <c r="L10" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="28.2">
       <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="D11" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>31</v>
-      </c>
       <c r="E11" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
+        <v>227</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>329</v>
+      </c>
       <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+      <c r="I11" s="28"/>
       <c r="J11" s="2"/>
       <c r="K11" s="3"/>
       <c r="L11" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="28.2">
       <c r="B12" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="F12" s="19" t="s">
         <v>236</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>239</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+      <c r="I12" s="28"/>
       <c r="J12" s="2"/>
       <c r="K12" s="3"/>
       <c r="L12" s="4"/>
@@ -1783,389 +2132,443 @@
     </row>
     <row r="13" spans="1:13" ht="28.2">
       <c r="B13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>34</v>
-      </c>
       <c r="E13" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
+        <v>228</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>330</v>
+      </c>
       <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="I13" s="28"/>
       <c r="J13" s="2"/>
       <c r="K13" s="3"/>
       <c r="L13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M13" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="28.2">
       <c r="B14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="D14" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>38</v>
-      </c>
       <c r="E14" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
+        <v>229</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>331</v>
+      </c>
       <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="I14" s="28"/>
       <c r="J14" s="2"/>
       <c r="K14" s="3"/>
       <c r="L14" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="28.2">
       <c r="B15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D15" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>41</v>
-      </c>
       <c r="E15" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
+        <v>230</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>332</v>
+      </c>
       <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="I15" s="28"/>
       <c r="J15" s="2"/>
       <c r="K15" s="3"/>
       <c r="L15" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="28.2">
       <c r="B16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>44</v>
-      </c>
       <c r="E16" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
+        <v>231</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>333</v>
+      </c>
       <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
+      <c r="I16" s="28"/>
       <c r="J16" s="2"/>
       <c r="K16" s="3"/>
       <c r="L16" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="2:13" ht="28.2">
       <c r="B17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="D17" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>47</v>
-      </c>
       <c r="E17" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
+        <v>232</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="G17" s="19"/>
       <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+      <c r="I17" s="28"/>
       <c r="J17" s="2"/>
       <c r="K17" s="3"/>
       <c r="L17" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="2:13" ht="28.2">
       <c r="B18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="D18" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>50</v>
-      </c>
       <c r="E18" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
+        <v>246</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>334</v>
+      </c>
       <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
+      <c r="I18" s="28"/>
       <c r="J18" s="2"/>
       <c r="K18" s="3"/>
       <c r="L18" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="2:13" ht="28.2">
       <c r="B19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>53</v>
-      </c>
       <c r="E19" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
+        <v>247</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>335</v>
+      </c>
       <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
+      <c r="I19" s="28"/>
       <c r="J19" s="2"/>
       <c r="K19" s="3"/>
       <c r="L19" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="2:13" ht="28.2">
       <c r="B20" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="D20" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="F20" s="6"/>
+        <v>188</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="F20" s="33" t="s">
+        <v>292</v>
+      </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
+      <c r="I20" s="50"/>
       <c r="J20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K20" s="7" t="s">
         <v>56</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>57</v>
       </c>
       <c r="L20" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="2:13" ht="28.2">
       <c r="B21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="D21" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>60</v>
-      </c>
       <c r="E21" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
+        <v>248</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>336</v>
+      </c>
       <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
+      <c r="I21" s="28"/>
       <c r="J21" s="2"/>
       <c r="K21" s="3"/>
       <c r="L21" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="2:13" ht="28.2">
       <c r="B22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="D22" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="C22" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="D22" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22" s="28" t="s">
-        <v>252</v>
-      </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
+      <c r="E22" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="F22" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="G22" s="33" t="s">
+        <v>337</v>
+      </c>
       <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
+      <c r="I22" s="50"/>
       <c r="J22" s="8"/>
       <c r="K22" s="9"/>
       <c r="L22" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="2:13" ht="28.2">
       <c r="B23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="D23" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="C23" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="E23" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
+      <c r="E23" s="33" t="s">
+        <v>250</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="G23" s="33" t="s">
+        <v>338</v>
+      </c>
       <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
+      <c r="I23" s="50"/>
       <c r="J23" s="8"/>
       <c r="K23" s="9"/>
       <c r="L23" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="2:13" ht="28.2">
       <c r="B24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="D24" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>69</v>
-      </c>
       <c r="E24" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
+        <v>251</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>339</v>
+      </c>
       <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
+      <c r="I24" s="28"/>
       <c r="J24" s="2"/>
       <c r="K24" s="3"/>
       <c r="L24" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="2:13" ht="28.2">
       <c r="B25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="D25" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>72</v>
-      </c>
       <c r="E25" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
+        <v>252</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>340</v>
+      </c>
       <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+      <c r="I25" s="28"/>
       <c r="J25" s="2"/>
       <c r="K25" s="3"/>
       <c r="L25" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="2:13" ht="28.2">
       <c r="B26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="D26" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>75</v>
-      </c>
       <c r="E26" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
+        <v>253</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>341</v>
+      </c>
       <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
+      <c r="I26" s="28"/>
       <c r="J26" s="2"/>
       <c r="K26" s="3"/>
       <c r="L26" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="2:13" ht="28.2">
       <c r="B27" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="D27" s="24" t="s">
         <v>240</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>243</v>
       </c>
       <c r="E27" s="1">
         <v>635</v>
       </c>
-      <c r="F27" s="1"/>
+      <c r="F27" s="19" t="s">
+        <v>297</v>
+      </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
+      <c r="I27" s="28"/>
       <c r="J27" s="2"/>
       <c r="K27" s="3"/>
       <c r="L27" s="4"/>
@@ -2173,21 +2576,23 @@
     </row>
     <row r="28" spans="2:13" ht="28.2">
       <c r="B28" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E28" s="1">
         <v>636</v>
       </c>
-      <c r="F28" s="1"/>
+      <c r="F28" s="19" t="s">
+        <v>298</v>
+      </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
+      <c r="I28" s="28"/>
       <c r="J28" s="2"/>
       <c r="K28" s="3"/>
       <c r="L28" s="4"/>
@@ -2195,21 +2600,23 @@
     </row>
     <row r="29" spans="2:13" ht="28.2">
       <c r="B29" s="2" t="s">
-        <v>217</v>
+        <v>342</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>210</v>
+        <v>181</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>221</v>
+        <v>345</v>
       </c>
       <c r="E29" s="1">
-        <v>639</v>
-      </c>
-      <c r="F29" s="1"/>
+        <v>637</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>344</v>
+      </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+      <c r="I29" s="28"/>
       <c r="J29" s="2"/>
       <c r="K29" s="3"/>
       <c r="L29" s="4"/>
@@ -2217,47 +2624,45 @@
     </row>
     <row r="30" spans="2:13" ht="28.2">
       <c r="B30" s="2" t="s">
-        <v>77</v>
+        <v>343</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>195</v>
+        <v>242</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="F30" s="1"/>
+        <v>346</v>
+      </c>
+      <c r="E30" s="1">
+        <v>638</v>
+      </c>
+      <c r="F30" s="19"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
+      <c r="I30" s="28"/>
       <c r="J30" s="2"/>
       <c r="K30" s="3"/>
-      <c r="L30" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>79</v>
-      </c>
+      <c r="L30" s="4"/>
+      <c r="M30" s="5"/>
     </row>
     <row r="31" spans="2:13" ht="28.2">
       <c r="B31" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="D31" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="C31" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="D31" s="24" t="s">
-        <v>220</v>
-      </c>
       <c r="E31" s="1">
-        <v>641</v>
-      </c>
-      <c r="F31" s="1"/>
+        <v>639</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>299</v>
+      </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
+      <c r="I31" s="28"/>
       <c r="J31" s="2"/>
       <c r="K31" s="3"/>
       <c r="L31" s="4"/>
@@ -2265,941 +2670,1061 @@
     </row>
     <row r="32" spans="2:13" ht="28.2">
       <c r="B32" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="E32" s="1">
-        <v>642</v>
-      </c>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
+        <v>77</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>347</v>
+      </c>
       <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
+      <c r="I32" s="28"/>
       <c r="J32" s="2"/>
       <c r="K32" s="3"/>
       <c r="L32" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="2:13" ht="28.2">
       <c r="B33" s="2" t="s">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="E33" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="F33" s="1"/>
+        <v>217</v>
+      </c>
+      <c r="E33" s="1">
+        <v>641</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>301</v>
+      </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
+      <c r="I33" s="28"/>
       <c r="J33" s="2"/>
       <c r="K33" s="3"/>
-      <c r="L33" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="M33" s="5" t="s">
-        <v>85</v>
-      </c>
+      <c r="L33" s="4"/>
+      <c r="M33" s="5"/>
     </row>
     <row r="34" spans="2:13" ht="28.2">
       <c r="B34" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
+        <v>80</v>
+      </c>
+      <c r="E34" s="1">
+        <v>642</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>348</v>
+      </c>
       <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
+      <c r="I34" s="28"/>
       <c r="J34" s="2"/>
       <c r="K34" s="3"/>
       <c r="L34" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="2:13" ht="28.2">
       <c r="B35" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="E35" s="1">
-        <v>644</v>
-      </c>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
+        <v>83</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>349</v>
+      </c>
       <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
+      <c r="I35" s="28"/>
       <c r="J35" s="2"/>
       <c r="K35" s="3"/>
       <c r="L35" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="2:13" ht="28.2">
-      <c r="B36" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="D36" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="E36" s="28" t="s">
-        <v>258</v>
-      </c>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="K36" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="B36" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="3"/>
       <c r="L36" s="4" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="2:13" ht="28.2">
-      <c r="B37" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="D37" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="E37" s="28" t="s">
-        <v>258</v>
-      </c>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="K37" s="7" t="s">
-        <v>97</v>
-      </c>
+      <c r="B37" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="E37" s="1">
+        <v>644</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H37" s="1"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="3"/>
       <c r="L37" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="2:13" ht="28.2">
-      <c r="B38" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="D38" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="E38" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="3"/>
+      <c r="B38" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="D38" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="E38" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="F38" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="H38" s="6"/>
+      <c r="I38" s="50"/>
+      <c r="J38" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>93</v>
+      </c>
       <c r="L38" s="4" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="2:13" ht="28.2">
-      <c r="B39" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C39" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="E39" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="3"/>
+      <c r="B39" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C39" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="D39" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="E39" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="F39" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="50"/>
+      <c r="J39" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>96</v>
+      </c>
       <c r="L39" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="2:13" ht="28.2">
-      <c r="B40" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="C40" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="D40" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="E40" s="28" t="s">
-        <v>260</v>
-      </c>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="K40" s="10" t="s">
-        <v>94</v>
-      </c>
+      <c r="B40" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="D40" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>308</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="H40" s="1"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="3"/>
       <c r="L40" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="2:13" ht="28.2">
       <c r="B41" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
+        <v>257</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>354</v>
+      </c>
       <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
+      <c r="I41" s="28"/>
       <c r="J41" s="2"/>
       <c r="K41" s="3"/>
       <c r="L41" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="2:13" ht="28.2">
       <c r="B42" s="8" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="D42" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="E42" s="28" t="s">
-        <v>263</v>
-      </c>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
+        <v>199</v>
+      </c>
+      <c r="D42" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="E42" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="F42" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>355</v>
+      </c>
       <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="2" t="s">
-        <v>10</v>
+      <c r="I42" s="50"/>
+      <c r="J42" s="8" t="s">
+        <v>92</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>111</v>
+        <v>7</v>
       </c>
       <c r="M42" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" spans="2:13" ht="28.2">
-      <c r="B43" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="C43" s="39" t="s">
-        <v>205</v>
-      </c>
-      <c r="D43" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="E43" s="28" t="s">
-        <v>263</v>
-      </c>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K43" s="10" t="s">
-        <v>114</v>
-      </c>
+      <c r="B43" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="D43" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="H43" s="1"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="3"/>
       <c r="L43" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M43" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" ht="28.2">
+      <c r="B44" s="8" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" ht="28.2">
-      <c r="B44" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C44" s="21" t="s">
-        <v>206</v>
-      </c>
-      <c r="D44" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="E44" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="3"/>
+      <c r="C44" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="D44" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="E44" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="F44" s="33" t="s">
+        <v>312</v>
+      </c>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K44" s="10" t="s">
+        <v>11</v>
+      </c>
       <c r="L44" s="4" t="s">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="M44" s="5" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="2:13" ht="28.2">
-      <c r="B45" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C45" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="D45" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="E45" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="3"/>
+      <c r="B45" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" s="45" t="s">
+        <v>202</v>
+      </c>
+      <c r="D45" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="E45" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="F45" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="50"/>
+      <c r="J45" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="K45" s="10" t="s">
+        <v>113</v>
+      </c>
       <c r="L45" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M45" s="5" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="2:13" ht="28.2">
-      <c r="B46" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="C46" s="22" t="s">
-        <v>208</v>
-      </c>
-      <c r="D46" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="E46" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="8"/>
-      <c r="K46" s="9"/>
+      <c r="B46" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="D46" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="H46" s="1"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="3"/>
       <c r="L46" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="2:13" ht="28.2">
-      <c r="B47" s="2"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" s="28" t="s">
-        <v>267</v>
-      </c>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="9"/>
+      <c r="B47" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C47" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="D47" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="H47" s="1"/>
+      <c r="I47" s="28"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="3"/>
       <c r="L47" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="2:13" ht="28.2">
       <c r="B48" s="8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="D48" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="E48" s="28" t="s">
-        <v>265</v>
-      </c>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
+        <v>205</v>
+      </c>
+      <c r="D48" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="E48" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="F48" s="33" t="s">
+        <v>316</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>359</v>
+      </c>
       <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
+      <c r="I48" s="50"/>
       <c r="J48" s="8"/>
       <c r="K48" s="9"/>
       <c r="L48" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="2:13" ht="28.2">
       <c r="B49" s="2"/>
       <c r="C49" s="21"/>
-      <c r="D49" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="E49" s="28" t="s">
-        <v>268</v>
+      <c r="D49" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" s="33" t="s">
+        <v>264</v>
       </c>
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
+      <c r="I49" s="50"/>
       <c r="J49" s="8"/>
       <c r="K49" s="9"/>
       <c r="L49" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="2:13" ht="28.2">
-      <c r="B50" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C50" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="D50" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="E50" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="3"/>
+      <c r="B50" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="D50" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="E50" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="F50" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="50"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="9"/>
       <c r="L50" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="2:13" ht="28.2">
-      <c r="B51" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="D51" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="E51" s="28" t="s">
-        <v>269</v>
+      <c r="B51" s="2"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="E51" s="33" t="s">
+        <v>265</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
+      <c r="I51" s="50"/>
       <c r="J51" s="8"/>
       <c r="K51" s="9"/>
       <c r="L51" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M51" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="2:13" ht="28.2">
-      <c r="B52" s="2"/>
-      <c r="C52" s="21"/>
-      <c r="D52" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="28" t="s">
-        <v>267</v>
-      </c>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="8"/>
-      <c r="K52" s="9"/>
+      <c r="B52" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C52" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="D52" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="3"/>
       <c r="L52" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M52" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="2:13" ht="28.2">
       <c r="B53" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="D53" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="E53" s="28" t="s">
-        <v>269</v>
-      </c>
-      <c r="F53" s="6"/>
+        <v>208</v>
+      </c>
+      <c r="D53" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="E53" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F53" s="33" t="s">
+        <v>318</v>
+      </c>
       <c r="G53" s="6"/>
       <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K53" s="7" t="s">
-        <v>130</v>
-      </c>
+      <c r="I53" s="50"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="9"/>
       <c r="L53" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M53" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="2:13" ht="28.2">
-      <c r="B54" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C54" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="D54" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="E54" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="3"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="50"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="9"/>
       <c r="L54" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M54" s="5" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="2:13" ht="28.2">
-      <c r="B55" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C55" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="D55" s="32" t="s">
-        <v>136</v>
-      </c>
-      <c r="E55" s="28" t="s">
-        <v>271</v>
-      </c>
-      <c r="F55" s="6"/>
+      <c r="B55" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C55" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="D55" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="E55" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F55" s="33" t="s">
+        <v>319</v>
+      </c>
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="9"/>
+      <c r="I55" s="50"/>
+      <c r="J55" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>129</v>
+      </c>
       <c r="L55" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M55" s="5" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="2:13" ht="28.2">
-      <c r="B56" s="2"/>
-      <c r="C56" s="21"/>
-      <c r="D56" s="25"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
+      <c r="B56" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="D56" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="F56" s="19" t="s">
+        <v>320</v>
+      </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="K56" s="13" t="s">
-        <v>139</v>
-      </c>
+      <c r="I56" s="28"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="3"/>
       <c r="L56" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M56" s="5" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57" spans="2:13" ht="28.2">
-      <c r="B57" s="2"/>
-      <c r="C57" s="21"/>
-      <c r="D57" s="33"/>
-      <c r="E57" s="29"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="K57" s="13" t="s">
-        <v>142</v>
-      </c>
+      <c r="B57" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D57" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="E57" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="F57" s="33" t="s">
+        <v>321</v>
+      </c>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="50"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="9"/>
       <c r="L57" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58" spans="2:13" ht="28.2">
-      <c r="B58" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C58" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="D58" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="E58" s="19" t="s">
-        <v>272</v>
-      </c>
+      <c r="B58" s="2"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="3"/>
+      <c r="I58" s="28"/>
+      <c r="J58" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="K58" s="13" t="s">
+        <v>138</v>
+      </c>
       <c r="L58" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="59" spans="2:13" ht="28.2">
-      <c r="B59" s="2" t="s">
-        <v>147</v>
-      </c>
+      <c r="B59" s="2"/>
       <c r="C59" s="21"/>
-      <c r="D59" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="E59" s="1">
-        <v>614</v>
-      </c>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="3"/>
+      <c r="D59" s="39"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="35"/>
+      <c r="H59" s="35"/>
+      <c r="I59" s="31"/>
+      <c r="J59" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K59" s="13" t="s">
+        <v>141</v>
+      </c>
       <c r="L59" s="4" t="s">
         <v>7</v>
       </c>
       <c r="M59" s="5" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60" spans="2:13" ht="28.2">
-      <c r="B60" s="2"/>
-      <c r="C60" s="21"/>
-      <c r="D60" s="34"/>
-      <c r="E60" s="30"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K60" s="13" t="s">
-        <v>151</v>
-      </c>
+      <c r="B60" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C60" s="46" t="s">
+        <v>212</v>
+      </c>
+      <c r="D60" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="E60" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="28"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="3"/>
       <c r="L60" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="M60" s="15" t="s">
-        <v>153</v>
+        <v>7</v>
+      </c>
+      <c r="M60" s="5" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="61" spans="2:13" ht="28.2">
       <c r="B61" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C61" s="21"/>
+      <c r="D61" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E61" s="1">
+        <v>614</v>
+      </c>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="28"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="3"/>
+      <c r="L61" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M61" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13" ht="28.2">
+      <c r="B62" s="2"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="40"/>
+      <c r="E62" s="36"/>
+      <c r="F62" s="14"/>
+      <c r="G62" s="36"/>
+      <c r="H62" s="36"/>
+      <c r="I62" s="32"/>
+      <c r="J62" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="K62" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="M62" s="15" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" ht="28.2">
+      <c r="B63" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C61" s="21"/>
-      <c r="D61" s="35" t="s">
+      <c r="C63" s="21"/>
+      <c r="D63" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="E61" s="31" t="s">
-        <v>267</v>
-      </c>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12"/>
-      <c r="I61" s="12"/>
-      <c r="J61" s="2" t="s">
+      <c r="E63" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="F63" s="12"/>
+      <c r="G63" s="35"/>
+      <c r="H63" s="35"/>
+      <c r="I63" s="31"/>
+      <c r="J63" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="K63" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="K61" s="13" t="s">
+      <c r="L63" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="M63" s="15" t="s">
         <v>155</v>
-      </c>
-      <c r="L61" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="M61" s="15" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="62" spans="2:13" ht="28.2">
-      <c r="B62" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C62" s="21"/>
-      <c r="D62" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="E62" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="F62" s="12"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="12"/>
-      <c r="I62" s="12"/>
-      <c r="J62" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="K62" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="L62" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="M62" s="15" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="63" spans="2:13" ht="28.2">
-      <c r="B63" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C63" s="22"/>
-      <c r="D63" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="E63" s="20" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="64" spans="2:13" ht="28.2">
       <c r="B64" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C64" s="21"/>
+      <c r="D64" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="C64" s="21"/>
-      <c r="D64" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="E64" s="20" t="s">
-        <v>274</v>
+      <c r="E64" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="F64" s="12"/>
+      <c r="G64" s="35"/>
+      <c r="H64" s="35"/>
+      <c r="I64" s="31"/>
+      <c r="J64" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K64" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="M64" s="15" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="65" spans="2:5" ht="28.2">
       <c r="B65" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C65" s="22"/>
+      <c r="D65" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="C65" s="22"/>
-      <c r="D65" s="36" t="s">
-        <v>94</v>
-      </c>
       <c r="E65" s="20" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="28.2">
       <c r="B66" s="2" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="C66" s="21"/>
-      <c r="D66" s="36" t="s">
-        <v>11</v>
+      <c r="D66" s="41" t="s">
+        <v>96</v>
       </c>
       <c r="E66" s="20" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="67" spans="2:5" ht="28.2">
-      <c r="B67" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="C67" s="23"/>
-      <c r="D67" s="36" t="s">
-        <v>114</v>
+      <c r="B67" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="42" t="s">
+        <v>93</v>
       </c>
       <c r="E67" s="20" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
     </row>
     <row r="68" spans="2:5" ht="28.2">
       <c r="B68" s="2" t="s">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="C68" s="21"/>
-      <c r="D68" s="35" t="s">
-        <v>130</v>
+      <c r="D68" s="42" t="s">
+        <v>11</v>
       </c>
       <c r="E68" s="20" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="69" spans="2:5" ht="28.2">
-      <c r="B69" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C69" s="21"/>
-      <c r="D69" s="37" t="s">
-        <v>139</v>
+      <c r="B69" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C69" s="23"/>
+      <c r="D69" s="42" t="s">
+        <v>113</v>
       </c>
       <c r="E69" s="20" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="70" spans="2:5" ht="28.2">
       <c r="B70" s="2" t="s">
-        <v>141</v>
+        <v>92</v>
       </c>
       <c r="C70" s="21"/>
-      <c r="D70" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="E70" s="20">
-        <v>656</v>
+      <c r="D70" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="E70" s="20" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="71" spans="2:5" ht="28.2">
       <c r="B71" s="2" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="C71" s="21"/>
-      <c r="D71" s="37" t="s">
-        <v>151</v>
+      <c r="D71" s="43" t="s">
+        <v>138</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="72" spans="2:5" ht="28.2">
       <c r="B72" s="2" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="C72" s="21"/>
-      <c r="D72" s="37" t="s">
-        <v>155</v>
+      <c r="D72" s="43" t="s">
+        <v>141</v>
       </c>
       <c r="E72" s="20">
-        <v>650</v>
+        <v>656</v>
       </c>
     </row>
     <row r="73" spans="2:5" ht="28.2">
       <c r="B73" s="2" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C73" s="21"/>
-      <c r="D73" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="E73" s="20">
+      <c r="D73" s="43" t="s">
+        <v>150</v>
+      </c>
+      <c r="E73" s="20" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" ht="28.2">
+      <c r="B74" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C74" s="21"/>
+      <c r="D74" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="E74" s="20">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" ht="28.2">
+      <c r="B75" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C75" s="21"/>
+      <c r="D75" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="E75" s="20">
         <v>650</v>
       </c>
     </row>
@@ -3207,4 +3732,1476 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H76"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="20.109375" style="20" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" style="20" customWidth="1"/>
+    <col min="3" max="3" width="22" style="29" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" style="20" customWidth="1"/>
+    <col min="5" max="5" width="19.21875" customWidth="1"/>
+    <col min="6" max="8" width="29.109375" style="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="52" customFormat="1">
+      <c r="A1" s="51" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.6">
+      <c r="A2" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="28.2">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>169</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1">
+        <v>627</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="28.2">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>277</v>
+      </c>
+      <c r="D4" s="20">
+        <v>101</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="28.2">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>276</v>
+      </c>
+      <c r="C5" s="48" t="s">
+        <v>278</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>362</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="28.2">
+      <c r="A6" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="1">
+        <v>628</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="28.2">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" ht="28.2">
+      <c r="A8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>326</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" ht="28.2">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" ht="28.2">
+      <c r="A10" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" ht="28.2">
+      <c r="A11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" ht="28.2">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" ht="28.2">
+      <c r="A13" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" ht="28.2">
+      <c r="A14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>330</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" ht="28.2">
+      <c r="A15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" ht="28.2">
+      <c r="A16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" ht="28.2">
+      <c r="A17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:8" ht="28.2">
+      <c r="A18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="F18" s="19"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" ht="28.2">
+      <c r="A19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:8" ht="28.2">
+      <c r="A20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" ht="28.2">
+      <c r="A21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="1:8" ht="28.2">
+      <c r="A22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" ht="28.2">
+      <c r="A23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>337</v>
+      </c>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+    </row>
+    <row r="24" spans="1:8" ht="28.2">
+      <c r="A24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" s="33" t="s">
+        <v>250</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="F24" s="33" t="s">
+        <v>338</v>
+      </c>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+    </row>
+    <row r="25" spans="1:8" ht="28.2">
+      <c r="A25" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:8" ht="28.2">
+      <c r="A26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" spans="1:8" ht="28.2">
+      <c r="A27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:8" ht="28.2">
+      <c r="A28" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="D28" s="1">
+        <v>635</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" spans="1:8" ht="28.2">
+      <c r="A29" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="D29" s="1">
+        <v>636</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="1:8" ht="28.2">
+      <c r="A30" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>345</v>
+      </c>
+      <c r="D30" s="1">
+        <v>637</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" spans="1:8" ht="28.2">
+      <c r="A31" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="D31" s="1">
+        <v>638</v>
+      </c>
+      <c r="E31" s="19"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="1:8" ht="28.2">
+      <c r="A32" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="D32" s="1">
+        <v>639</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" spans="1:8" ht="28.2">
+      <c r="A33" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="1:8" ht="28.2">
+      <c r="A34" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="D34" s="1">
+        <v>641</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:8" ht="28.2">
+      <c r="A35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="1">
+        <v>642</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="1:8" ht="28.2">
+      <c r="A36" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="1:8" ht="28.2">
+      <c r="A37" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="1:8" ht="28.2">
+      <c r="A38" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="1">
+        <v>644</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" spans="1:8" ht="28.2">
+      <c r="A39" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="C39" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D39" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="E39" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+    </row>
+    <row r="40" spans="1:8" ht="28.2">
+      <c r="A40" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="C40" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="E40" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+    </row>
+    <row r="41" spans="1:8" ht="28.2">
+      <c r="A41" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="D41" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>308</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" spans="1:8" ht="28.2">
+      <c r="A42" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" spans="1:8" ht="28.2">
+      <c r="A43" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="C43" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="E43" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+    </row>
+    <row r="44" spans="1:8" ht="28.2">
+      <c r="A44" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="D44" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+    </row>
+    <row r="45" spans="1:8" ht="28.2">
+      <c r="A45" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="C45" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="D45" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="E45" s="33" t="s">
+        <v>312</v>
+      </c>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+    </row>
+    <row r="46" spans="1:8" ht="28.2">
+      <c r="A46" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="B46" s="45" t="s">
+        <v>202</v>
+      </c>
+      <c r="C46" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="D46" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="E46" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+    </row>
+    <row r="47" spans="1:8" ht="28.2">
+      <c r="A47" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="C47" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="D47" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" spans="1:8" ht="28.2">
+      <c r="A48" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="C48" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" spans="1:8" ht="28.2">
+      <c r="A49" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B49" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="C49" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="D49" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="E49" s="33" t="s">
+        <v>316</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+    </row>
+    <row r="50" spans="1:8" ht="28.2">
+      <c r="A50" s="2"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+    </row>
+    <row r="51" spans="1:8" ht="28.2">
+      <c r="A51" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="B51" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="C51" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="D51" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="E51" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+    </row>
+    <row r="52" spans="1:8" ht="28.2">
+      <c r="A52" s="2"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="D52" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+    </row>
+    <row r="53" spans="1:8" ht="28.2">
+      <c r="A53" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="D53" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+    </row>
+    <row r="54" spans="1:8" ht="28.2">
+      <c r="A54" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="C54" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="D54" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="E54" s="33" t="s">
+        <v>318</v>
+      </c>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+    </row>
+    <row r="55" spans="1:8" ht="28.2">
+      <c r="A55" s="2"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+    </row>
+    <row r="56" spans="1:8" ht="28.2">
+      <c r="A56" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B56" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="C56" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="D56" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="E56" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+    </row>
+    <row r="57" spans="1:8" ht="28.2">
+      <c r="A57" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="C57" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+    </row>
+    <row r="58" spans="1:8" ht="28.2">
+      <c r="A58" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="C58" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="D58" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="E58" s="33" t="s">
+        <v>321</v>
+      </c>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+    </row>
+    <row r="59" spans="1:8" ht="28.2">
+      <c r="A59" s="2"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="25"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+    </row>
+    <row r="60" spans="1:8" ht="28.2">
+      <c r="A60" s="2"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="39"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="35"/>
+      <c r="G60" s="35"/>
+      <c r="H60" s="35"/>
+    </row>
+    <row r="61" spans="1:8" ht="28.2">
+      <c r="A61" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B61" s="46" t="s">
+        <v>212</v>
+      </c>
+      <c r="C61" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D61" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+    </row>
+    <row r="62" spans="1:8" ht="28.2">
+      <c r="A62" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B62" s="21"/>
+      <c r="C62" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D62" s="1">
+        <v>614</v>
+      </c>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+    </row>
+    <row r="63" spans="1:8" ht="28.2">
+      <c r="A63" s="2"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="40"/>
+      <c r="D63" s="36"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="36"/>
+      <c r="G63" s="36"/>
+      <c r="H63" s="36"/>
+    </row>
+    <row r="64" spans="1:8" ht="28.2">
+      <c r="A64" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B64" s="21"/>
+      <c r="C64" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="E64" s="12"/>
+      <c r="F64" s="35"/>
+      <c r="G64" s="35"/>
+      <c r="H64" s="35"/>
+    </row>
+    <row r="65" spans="1:8" ht="28.2">
+      <c r="A65" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B65" s="21"/>
+      <c r="C65" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="D65" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="E65" s="12"/>
+      <c r="F65" s="35"/>
+      <c r="G65" s="35"/>
+      <c r="H65" s="35"/>
+    </row>
+    <row r="66" spans="1:8" ht="28.2">
+      <c r="A66" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B66" s="22"/>
+      <c r="C66" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="D66" s="20" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="28.2">
+      <c r="A67" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B67" s="21"/>
+      <c r="C67" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="D67" s="20" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="28.2">
+      <c r="A68" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B68" s="22"/>
+      <c r="C68" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="D68" s="20" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="28.2">
+      <c r="A69" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B69" s="21"/>
+      <c r="C69" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="D69" s="20" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="28.2">
+      <c r="A70" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B70" s="23"/>
+      <c r="C70" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="D70" s="20" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="28.2">
+      <c r="A71" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B71" s="21"/>
+      <c r="C71" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="D71" s="20" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="28.2">
+      <c r="A72" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B72" s="21"/>
+      <c r="C72" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="D72" s="20" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="28.2">
+      <c r="A73" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B73" s="21"/>
+      <c r="C73" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="D73" s="20">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="28.2">
+      <c r="A74" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B74" s="21"/>
+      <c r="C74" s="43" t="s">
+        <v>150</v>
+      </c>
+      <c r="D74" s="20" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="28.2">
+      <c r="A75" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B75" s="21"/>
+      <c r="C75" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="D75" s="20">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="28.2">
+      <c r="A76" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B76" s="21"/>
+      <c r="C76" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="D76" s="20">
+        <v>650</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>